--- a/exc.xlsx
+++ b/exc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365changwon-my.sharepoint.com/personal/y2012222_staff_changwon_ac_kr/Documents/바탕 화면/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365changwon-my.sharepoint.com/personal/y2012222_staff_changwon_ac_kr/Documents/바탕 화면/JASAel리뷰/gittest/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C404EC7C-5EFE-4914-B50F-E7BE5B3BF602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{C404EC7C-5EFE-4914-B50F-E7BE5B3BF602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D47BA4AA-0539-40D0-B7D0-6F5C5A3766C2}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{07EE39D8-333D-4557-A09F-2ED6A8457367}"/>
   </bookViews>
@@ -426,10 +426,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A19D8B87-973A-4318-9901-30614B535CF1}">
-  <dimension ref="H6"/>
+  <dimension ref="B3:H6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="6" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="H6" t="s">
         <v>0</v>
       </c>
